--- a/experiment/ELAN_bestx2/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/ELAN_bestx2/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.86</v>
+        <v>33.05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8477</v>
+        <v>0.9086</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.53</v>
+        <v>32.93</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8911</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.42</v>
+        <v>28.49</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8068</v>
+        <v>0.8913</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.28</v>
+        <v>31.16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9207</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.47</v>
+        <v>37.13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9559</v>
+        <v>0.9874000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.36</v>
+        <v>25.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8206</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.39</v>
+        <v>35.96</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9417</v>
+        <v>0.9656</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.62</v>
+        <v>27.04</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8163</v>
+        <v>0.9054</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35.74</v>
+        <v>40.26</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9477</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.98</v>
+        <v>34.62</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8981</v>
+        <v>0.9665</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22.01</v>
+        <v>26.6</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.9426</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25.98</v>
+        <v>29.13</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8396</v>
+        <v>0.9167999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.93</v>
+        <v>34.81</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8946</v>
+        <v>0.9428</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23.59</v>
+        <v>25.99</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7811</v>
+        <v>0.8767</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.59</v>
+        <v>31.01</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7957</v>
+        <v>0.8587</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.69</v>
+        <v>37.47</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9322</v>
+        <v>0.9634</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27.99</v>
+        <v>31.76</v>
       </c>
       <c r="C18" t="n">
-        <v>0.903</v>
+        <v>0.9564</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.98</v>
+        <v>29.83</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8665</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23.54</v>
+        <v>28.61</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8768</v>
+        <v>0.9475</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.15</v>
+        <v>27.37</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8685</v>
+        <v>0.9127</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32.76</v>
+        <v>34.37</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8986</v>
+        <v>0.9199000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28.04</v>
+        <v>29.83</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8563</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.72</v>
+        <v>37.82</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9514</v>
+        <v>0.9812</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.87</v>
+        <v>26.69</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7929</v>
+        <v>0.8955</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30.32</v>
+        <v>37.8</v>
       </c>
       <c r="C26" t="n">
-        <v>0.912</v>
+        <v>0.9612000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.3</v>
+        <v>31.31</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7929</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.87</v>
+        <v>32.74</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.9183</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>33.18</v>
+        <v>37.28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9223</v>
+        <v>0.9497</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26.76</v>
+        <v>33.48</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8764</v>
+        <v>0.9656</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26.34</v>
+        <v>31.33</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.9571</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26.63</v>
+        <v>29.06</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8867</v>
+        <v>0.9373</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30.38</v>
+        <v>35.15</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9054</v>
+        <v>0.9597</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.66</v>
+        <v>32.98</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.9428</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.92</v>
+        <v>26.74</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7585</v>
+        <v>0.8114</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.24</v>
+        <v>34.97</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8911</v>
+        <v>0.9571</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30.43</v>
+        <v>35.08</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9296</v>
+        <v>0.9635</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30.54</v>
+        <v>34.01</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9304</v>
+        <v>0.9560999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.51</v>
+        <v>32.17</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8034</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.81</v>
+        <v>28.84</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24.55</v>
+        <v>35.37</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.9867</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.75</v>
+        <v>34.44</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9034</v>
+        <v>0.9721</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30.39</v>
+        <v>36.19</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9277</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27.84</v>
+        <v>38.39</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9288</v>
+        <v>0.9751</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>36.78</v>
+        <v>40.96</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9654</v>
+        <v>0.9833</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26.27</v>
+        <v>32.77</v>
       </c>
       <c r="C46" t="n">
-        <v>0.851</v>
+        <v>0.9523</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25.82</v>
+        <v>28.71</v>
       </c>
       <c r="C47" t="n">
-        <v>0.865</v>
+        <v>0.9323</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>23.71</v>
+        <v>27.5</v>
       </c>
       <c r="C48" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>22.47</v>
+        <v>27.31</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8872</v>
+        <v>0.9623</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24.99</v>
+        <v>29.14</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.9167</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27.82</v>
+        <v>30.45</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8723</v>
+        <v>0.9275</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.2</v>
+        <v>33.76</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9251</v>
+        <v>0.9607</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.38</v>
+        <v>35.68</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9029</v>
+        <v>0.9757</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24.38</v>
+        <v>27.64</v>
       </c>
       <c r="C54" t="n">
-        <v>0.846</v>
+        <v>0.9117</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23.2</v>
+        <v>25.31</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7874</v>
+        <v>0.8587</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31.21</v>
+        <v>37.84</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9419</v>
+        <v>0.9789</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>26.79</v>
+        <v>30.95</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8703</v>
+        <v>0.9422</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.39</v>
+        <v>38.15</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9297</v>
+        <v>0.9741</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28.31</v>
+        <v>34.26</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.41</v>
+        <v>29.38</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9184</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24.27</v>
+        <v>26.47</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7361</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>27.3</v>
+        <v>30.58</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8676</v>
+        <v>0.9369</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24.35</v>
+        <v>30.01</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8852</v>
+        <v>0.9655</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>23.45</v>
+        <v>26.42</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7086</v>
+        <v>0.7503</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>29.65</v>
+        <v>32.43</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9003</v>
+        <v>0.9388</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>28.6</v>
+        <v>31.18</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8818</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>24.53</v>
+        <v>25.61</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8086</v>
+        <v>0.8524</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>21.82</v>
+        <v>27.22</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9104</v>
+        <v>0.9746</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>33.31</v>
+        <v>38.04</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9403</v>
+        <v>0.9752999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27.06</v>
+        <v>29.68</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8671</v>
+        <v>0.9219000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>23.8</v>
+        <v>24.86</v>
       </c>
       <c r="C71" t="n">
-        <v>0.7541</v>
+        <v>0.7998</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>29.35</v>
+        <v>32.02</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8008</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>21.21</v>
+        <v>27.08</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8568</v>
+        <v>0.9605</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>24.06</v>
+        <v>26.1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8175</v>
+        <v>0.8767</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>25.58</v>
+        <v>29.32</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8232</v>
+        <v>0.9248</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.27</v>
+        <v>37.27</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9044</v>
+        <v>0.9503</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>26.91</v>
+        <v>31.28</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9059</v>
+        <v>0.9565</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>24.67</v>
+        <v>26.09</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8123</v>
+        <v>0.8659</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>31.02</v>
+        <v>34.02</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8965</v>
+        <v>0.9347</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>27.79</v>
+        <v>29.94</v>
       </c>
       <c r="C80" t="n">
-        <v>0.8262</v>
+        <v>0.8761</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>37.82</v>
+        <v>41.3</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9732</v>
+        <v>0.9854000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.83</v>
+        <v>43.64</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9746</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>34.5</v>
+        <v>38.9</v>
       </c>
       <c r="C83" t="n">
-        <v>0.959</v>
+        <v>0.9757</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>24.06</v>
+        <v>26.97</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8192</v>
+        <v>0.9034</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>31.59</v>
+        <v>34.59</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9097</v>
+        <v>0.9407</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>31.74</v>
+        <v>35.17</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9563</v>
+        <v>0.9787</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>33.74</v>
+        <v>36.92</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9436</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.53</v>
+        <v>35.2</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9005</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>22.38</v>
+        <v>24.44</v>
       </c>
       <c r="C89" t="n">
-        <v>0.77</v>
+        <v>0.8468</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>29.85</v>
+        <v>31.53</v>
       </c>
       <c r="C90" t="n">
-        <v>0.8672</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.72</v>
+        <v>45.13</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>26.54</v>
+        <v>29.45</v>
       </c>
       <c r="C92" t="n">
-        <v>0.833</v>
+        <v>0.9078000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>19.59</v>
+        <v>23.22</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.8421999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.72</v>
+        <v>37.61</v>
       </c>
       <c r="C94" t="n">
-        <v>0.95</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>28.87</v>
+        <v>31.48</v>
       </c>
       <c r="C95" t="n">
-        <v>0.8698</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>21.99</v>
+        <v>24.02</v>
       </c>
       <c r="C96" t="n">
-        <v>0.6829</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.96</v>
+        <v>32.61</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>26.85</v>
+        <v>29.98</v>
       </c>
       <c r="C98" t="n">
-        <v>0.855</v>
+        <v>0.9211</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>22.63</v>
+        <v>24.57</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7278</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.63</v>
+        <v>32.69</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.29</v>
+        <v>29.54</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8121</v>
+        <v>0.8773</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.69</v>
+        <v>31.9</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8676</v>
+        <v>0.9262</v>
       </c>
     </row>
   </sheetData>
